--- a/feedback_surveys/011_nonprofit_donor_communication_feedback_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/011_nonprofit_donor_communication_feedback_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -692,8 +692,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -721,12 +721,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option':_'email'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option': 'Email'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -738,12 +738,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option':_'social_media'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option': 'Social media'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -755,12 +755,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option':_'phone'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option': 'Phone'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -772,12 +772,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option':_'postal_mail'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option': 'Postal mail'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -789,12 +789,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option':_'less_than_once_a_week'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option': 'Less than once a week'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option':_'more_than_once_a_week'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option': 'More than once a week'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option':_'never'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option': 'Never'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -840,12 +840,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option':_'news'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option': 'News'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option':_'events'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option': 'Events'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -874,12 +874,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option':_'stories'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option': 'Stories'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -891,12 +891,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option':_'financial_reports'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option': 'Financial reports'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
